--- a/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Mathematik1.xlsx
+++ b/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Mathematik1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/131a8beddc4e0454/01JupyterAndCo/04GitHub/GitHubCloneMBP/richard4231.github.io/25-11-pdf-Analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{B8438B10-E4C4-4D4F-9FB5-D614576CD7D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED939068-65B3-6145-A25D-177041B19F98}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{B8438B10-E4C4-4D4F-9FB5-D614576CD7D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FACABBB-1171-404C-89DE-191951521FD3}"/>
   <bookViews>
     <workbookView xWindow="500" yWindow="620" windowWidth="26040" windowHeight="15880" xr2:uid="{AA5F5EE3-90A2-434A-ACDF-DF6694D14C9E}"/>
   </bookViews>
